--- a/generated-docs/Nof1_FormulationSchedule_SUB-2026-004_DRAFT.xlsx
+++ b/generated-docs/Nof1_FormulationSchedule_SUB-2026-004_DRAFT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="205">
   <si>
     <t>W Code</t>
   </si>
@@ -50,31 +50,94 @@
     <t>Evidence Pointer</t>
   </si>
   <si>
+    <t>W010003000</t>
+  </si>
+  <si>
+    <t>Ashwagandha</t>
+  </si>
+  <si>
+    <t>mg</t>
+  </si>
+  <si>
+    <t>Thyroid / Adaptogenic</t>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>Total cortisol 24.91 ug/gCR (low), Low Cortisol symptom 28.57%, Hypometabolism symptom 29.17%</t>
+  </si>
+  <si>
+    <t>Foundational adaptogen for the HPA-hypocortisolism pattern. Withania somnifera at 300 mg/day of a 10:1 extract aligns with the lower-end therapeutic range cited in RCT literature for HPA modulation, sleep and energy outcomes. Particularly appropriate where autonomic-arousal symptoms (palpitations, nervousness) coexist with low cortisol, as Withania is generally non-stimulating.</t>
+  </si>
+  <si>
+    <t>Practitioner to assess thyroid status given Withania's reported effects on thyroid markers; assess any autoimmune/immune-modulating considerations.</t>
+  </si>
+  <si>
+    <t>RCT evidence (e.g. Salve 2019; Chandrasekhar 2012) supports practitioner consideration of ashwagandha for stress, cortisol-pattern modulation and sleep — clinical relevance for this patient is for practitioner assessment.</t>
+  </si>
+  <si>
+    <t>W010020000</t>
+  </si>
+  <si>
+    <t>Rhodiola rosea (Rose Root)</t>
+  </si>
+  <si>
+    <t>MODERATE</t>
+  </si>
+  <si>
+    <t>Total cortisol 24.91 ug/gCR (low), Hypometabolism symptom 29.17%</t>
+  </si>
+  <si>
+    <t>Conservative inclusion at 150 mg/day (10:1 extract) given the HPA-hypocortisolism context. Dose deliberately at the lower end of the therapeutic range due to the autonomic-arousal symptom overlay (palpitations, nervousness).</t>
+  </si>
+  <si>
+    <t>Practitioner caution: stimulating adaptogen — may exacerbate palpitations or insomnia in sensitive patients. Monitor symptoms after initiation.</t>
+  </si>
+  <si>
+    <t>Published trials (Olsson 2009; Darbinyan 2007) support practitioner consideration of Rhodiola for stress-related fatigue at 200–400 mg/day; conservative dose here reflects symptom overlay.</t>
+  </si>
+  <si>
+    <t>W010001000</t>
+  </si>
+  <si>
+    <t>American ginseng</t>
+  </si>
+  <si>
+    <t>Total cortisol 24.91 ug/gCR (low), Burned out / mental fatigue symptoms (MODERATE)</t>
+  </si>
+  <si>
+    <t>Panax quinquefolius selected over Panax ginseng for a generally less stimulating HPA support profile, appropriate where the patient has autonomic-arousal symptoms alongside hypocortisolism. 200 mg/day of a 4:1 extract is within the lower therapeutic range.</t>
+  </si>
+  <si>
+    <t>Practitioner to monitor for insomnia, blood pressure or blood sugar changes.</t>
+  </si>
+  <si>
+    <t>Published evidence (Barton 2013) supports practitioner consideration of American ginseng for fatigue states — clinical relevance for this patient is for practitioner assessment.</t>
+  </si>
+  <si>
     <t>W140019000</t>
   </si>
   <si>
     <t>DIM (3,3'-diindolylmethane)</t>
   </si>
   <si>
-    <t>mg</t>
-  </si>
-  <si>
     <t>Hormone Metabolism</t>
   </si>
   <si>
-    <t>STANDARD</t>
-  </si>
-  <si>
-    <t>2-OH Estrone 0.04 ug/gCR (low), 2-OH(E1+E2)/16-OHE1 0.60 (low), Estrogen Quotient 0.24 (low)</t>
-  </si>
-  <si>
-    <t>Foundational hormone_metabolism axis ingredient. Published literature supports DIM as a Phase I CYP1A1 modulator that may shift oestrogen hydroxylation toward the 2-OH pathway — for practitioner consideration given low 2-OH Estrone (0.04 ug/gCR, reference 0.10–1.88) and low 2-OH/16-OH ratio (0.60, reference 1.10–5.60).</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; published literature notes possible mild GI symptoms. The practitioner may wish to monitor and consider clinical correlation.</t>
-  </si>
-  <si>
-    <t>Library entry references for DIM and Phase I oestrogen pathway modulation per published mechanism studies.</t>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>2-OH Estrone 0.04 (low), 2-OH(E1+E2)/16-OH-E1 ratio 0.60 (low), Estrogen Dominance/Progesterone Deficiency symptom 33.33%</t>
+  </si>
+  <si>
+    <t>Primary inclusion for the 16-OH-dominant oestrogen Phase I pattern. DIM at 150 mg/day is within the standard therapeutic range and may support relative shift toward 2-OH pathway flux per published mechanism literature.</t>
+  </si>
+  <si>
+    <t>Practitioner to consider drug-interaction context (DIM and related compounds may influence CYP enzymes); monitor for headache/GI symptoms at higher doses.</t>
+  </si>
+  <si>
+    <t>Published mechanism studies (Bradlow et al.) suggest DIM influences CYP-mediated Phase I oestrogen pathway balance — clinical relevance for this patient is for practitioner assessment.</t>
   </si>
   <si>
     <t>W040012000</t>
@@ -83,106 +146,205 @@
     <t>Calcium D-glucarate</t>
   </si>
   <si>
-    <t>Estrogen Quotient 0.24 (low), 16-OH-dominant pattern</t>
-  </si>
-  <si>
-    <t>Supports glucuronidation pathway and inhibits beta-glucuronidase per published mechanism studies — for practitioner consideration of enterohepatic clearance of conjugated oestrogen metabolites, given low oestrogen quotient.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated. Provides ~80 mg elemental calcium per dose — practitioner may wish to consider in context of total dietary calcium.</t>
-  </si>
-  <si>
-    <t>Library entry references for calcium D-glucarate and glucuronidation/beta-glucuronidase pathway.</t>
+    <t>Phase II oestrogen clearance support (low 2-MeOH-E1 and 2-MeOH-E2), 16-OH dominant Phase I pattern</t>
+  </si>
+  <si>
+    <t>Supports Phase II oestrogen clearance via beta-glucuronidase inhibition per published mechanism literature, complementing the DIM-driven Phase I rebalancing.</t>
+  </si>
+  <si>
+    <t>Generally well tolerated; practitioner to consider co-administration timing if patient is on medications metabolised via glucuronidation.</t>
+  </si>
+  <si>
+    <t>Published mechanism literature describes calcium D-glucarate's inhibition of intestinal beta-glucuronidase, with potential implications for oestrogen and xenobiotic conjugate clearance — practitioner to assess.</t>
+  </si>
+  <si>
+    <t>W010019000</t>
+  </si>
+  <si>
+    <t>Resveratrol</t>
+  </si>
+  <si>
+    <t>Estrogen Dominance/Progesterone Deficiency symptom 33.33%, Metabolic Syndrome symptom 36.67%</t>
+  </si>
+  <si>
+    <t>Adjunct for the hormone_metabolism axis with literature describing aromatase modulation and Phase II support; also contributes to the antioxidant/redox load given the cardiometabolic symptom context.</t>
+  </si>
+  <si>
+    <t>Practitioner to consider potential interaction with anticoagulants per TGA-listed warnings.</t>
+  </si>
+  <si>
+    <t>Published in vitro and clinical work describes resveratrol's potential modulation of aromatase and broader cardiometabolic markers — practitioner to assess.</t>
   </si>
   <si>
     <t>W010013000</t>
   </si>
   <si>
-    <t>Milk thistle (silymarin)</t>
-  </si>
-  <si>
-    <t>Published literature supports silymarin as a Nrf2-mediated Phase II hepatic conjugation supporter — for practitioner consideration of hepatic oestrogen metabolism support.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; the practitioner may wish to consider in context of any liver medications.</t>
-  </si>
-  <si>
-    <t>Library entry references for silymarin and Phase II hepatoprotection.</t>
-  </si>
-  <si>
-    <t>W010019000</t>
-  </si>
-  <si>
-    <t>Resveratrol</t>
-  </si>
-  <si>
-    <t>MODERATE</t>
-  </si>
-  <si>
-    <t>Estrogen Quotient 0.24 (low), 2-OH Estrone (low)</t>
-  </si>
-  <si>
-    <t>Published literature supports resveratrol for mild aromatase modulation and 2-OH pathway support — for practitioner consideration alongside DIM for oestrogen metabolism balance. Dose at Library AUST L limit of 150 mg.</t>
-  </si>
-  <si>
-    <t>TGA-required label warning notes possible interaction with warfarin and other medications. The practitioner may wish to confirm no anticoagulant use before recommending. Not recommended during pregnancy or lactation (not applicable here — adult male).</t>
-  </si>
-  <si>
-    <t>Library entry references for resveratrol mechanism studies and oestrogen pathway modulation.</t>
-  </si>
-  <si>
-    <t>W010003000</t>
-  </si>
-  <si>
-    <t>Ashwagandha</t>
-  </si>
-  <si>
-    <t>Thyroid / Adaptogenic</t>
-  </si>
-  <si>
-    <t>Total 24hr Cortisol 24.91 ug/gCR (low), DHEA in lower portion of range</t>
-  </si>
-  <si>
-    <t>Foundational thyroid_adaptogenic axis ingredient. Published literature including double-blind RCT data supports ashwagandha for HPA resilience and stress modulation — for practitioner consideration given low total urinary cortisol pattern.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated. The practitioner may wish to consider in context of any thyroid medications, immunosuppressants, or sedatives.</t>
-  </si>
-  <si>
-    <t>Library entry references including Salve 2019 (Cureus) and related adaptogen RCTs.</t>
-  </si>
-  <si>
-    <t>W010020000</t>
-  </si>
-  <si>
-    <t>Rhodiola</t>
-  </si>
-  <si>
-    <t>Total 24hr Cortisol 24.91 ug/gCR (low)</t>
-  </si>
-  <si>
-    <t>Published literature supports rhodiola for stress-related fatigue and HPA modulation — complementary adaptogenic support alongside ashwagandha for the HPA-hypocortisolism pattern.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; insomnia possible if dosed late in day. The practitioner may wish to recommend morning dosing.</t>
-  </si>
-  <si>
-    <t>Library entry references including Olsson 2009 and Ishaque 2012 systematic review.</t>
-  </si>
-  <si>
-    <t>W010001000</t>
-  </si>
-  <si>
-    <t>American ginseng (Panax quinquefolius)</t>
-  </si>
-  <si>
-    <t>Published literature including cancer-related fatigue RCTs supports American ginseng as a tonic adaptogen — for practitioner consideration as adjunct to the adaptogen stack for HPA-hypocortisolism.</t>
-  </si>
-  <si>
-    <t>May affect blood pressure and glucose; the practitioner may wish to consider in context of any antihypertensive or glucose-lowering therapy.</t>
-  </si>
-  <si>
-    <t>Library entry references including Barton 2013 N07C2 trial.</t>
+    <t>Milk thistle</t>
+  </si>
+  <si>
+    <t>Phase II oestrogen support (low 2-MeOH metabolites), Hepatic clearance support context</t>
+  </si>
+  <si>
+    <t>Hepatic Phase II conjugation support via Nrf2-mediated glutathione pathway, complementing the oestrogen-clearance strategy. 150 mg/day of an 80% silymarin standardised extract.</t>
+  </si>
+  <si>
+    <t>Generally well tolerated; rare GI symptoms reported.</t>
+  </si>
+  <si>
+    <t>Published mechanism studies describe silymarin's Nrf2 induction and hepatoprotective effects — practitioner to assess.</t>
+  </si>
+  <si>
+    <t>W140010000</t>
+  </si>
+  <si>
+    <t>N-acetyl cysteine (NAC)</t>
+  </si>
+  <si>
+    <t>Antioxidant / Redox</t>
+  </si>
+  <si>
+    <t>Phase II oestrogen support, Antioxidant load for cardiometabolic context</t>
+  </si>
+  <si>
+    <t>Foundational antioxidant_redox inclusion. NAC supports glutathione synthesis and is described in published literature as relevant to conjugation/quenching of reactive oestrogen-quinone metabolites.</t>
+  </si>
+  <si>
+    <t>GI symptoms most common; long-term high-dose use may warrant trace mineral monitoring per published frameworks.</t>
+  </si>
+  <si>
+    <t>Published mechanism literature supports practitioner consideration of NAC for glutathione precursor activity and quinone quenching — clinical relevance for this patient is for practitioner assessment.</t>
+  </si>
+  <si>
+    <t>W010031000</t>
+  </si>
+  <si>
+    <t>Quercetin</t>
+  </si>
+  <si>
+    <t>4-OH Estrone (lower-limit reference) — CYP1B1 modulation, MODERATE high blood pressure symptom</t>
+  </si>
+  <si>
+    <t>Modulates CYP1B1 per published literature and provides broad antioxidant/anti-inflammatory support relevant to the cardiometabolic context.</t>
+  </si>
+  <si>
+    <t>Generally well tolerated at this dose.</t>
+  </si>
+  <si>
+    <t>Published mechanism studies describe quercetin's CYP1B1 modulation and Serban et al. meta-analysis describes BP-lowering effect — practitioner to assess clinical relevance.</t>
+  </si>
+  <si>
+    <t>W030008000</t>
+  </si>
+  <si>
+    <t>Methylcobalamin (Vitamin B12)</t>
+  </si>
+  <si>
+    <t>mcg</t>
+  </si>
+  <si>
+    <t>B-Vitamins / Methylation</t>
+  </si>
+  <si>
+    <t>Low 2-MeOH Estrone, low 2-MeOH Estradiol (substrate-limited Phase II methylation)</t>
+  </si>
+  <si>
+    <t>Methyl-donor cofactor support for the Phase II methylation/COMT context. 500 mcg is within standard therapeutic range.</t>
+  </si>
+  <si>
+    <t>Generally well tolerated.</t>
+  </si>
+  <si>
+    <t>Published frameworks support practitioner consideration of methylcobalamin as a methyl-donor cofactor for COMT-dependent oestrogen Phase II.</t>
+  </si>
+  <si>
+    <t>W030027000</t>
+  </si>
+  <si>
+    <t>Calcium folinate (Folinic acid)</t>
+  </si>
+  <si>
+    <t>Low Phase II methylated oestrogen output</t>
+  </si>
+  <si>
+    <t>Folate methyl-donor support at the Library-permitted maximum dose for in-pod use (corresponds to 500 mcg folinic acid, the AUST L per-dose limit for folate-equivalent ingredients).</t>
+  </si>
+  <si>
+    <t>Standard folate-supplementation considerations apply; practitioner to consider any B12-deficiency masking risk per published guidance.</t>
+  </si>
+  <si>
+    <t>Published frameworks describe folinic acid as a methyl-donor cofactor for COMT-dependent methylation pathways.</t>
+  </si>
+  <si>
+    <t>W030012000</t>
+  </si>
+  <si>
+    <t>Pyridoxal-5-phosphate (P5P / Vitamin B6)</t>
+  </si>
+  <si>
+    <t>Phase II methylation support context</t>
+  </si>
+  <si>
+    <t>P5P as the active B6 cofactor supports transsulfuration and broader methylation pathway flux. Dose corresponds to 5 mg elemental pyridoxine, well within TGA-relevant limits.</t>
+  </si>
+  <si>
+    <t>Practitioner to monitor for any sensory neuropathy symptoms at chronic high doses per TGA warnings; this dose is conservative.</t>
+  </si>
+  <si>
+    <t>Published frameworks support B6 as a methylation/transsulfuration cofactor.</t>
+  </si>
+  <si>
+    <t>W030004000</t>
+  </si>
+  <si>
+    <t>Pantothenic acid (Vitamin B5)</t>
+  </si>
+  <si>
+    <t>Total cortisol 24.91 ug/gCR (low), Burned out / fatigue symptoms</t>
+  </si>
+  <si>
+    <t>Classical adrenal cofactor for the HPA-hypocortisolism pattern per integrative medicine frameworks; provides CoA precursor support for adrenal steroidogenesis. ~200 mg/day delivered via 40 granules of the calcium pantothenate ingredient.</t>
+  </si>
+  <si>
+    <t>Published frameworks describe pantothenic acid's role in CoA synthesis and steroidogenesis — practitioner to assess clinical relevance.</t>
+  </si>
+  <si>
+    <t>W040002000</t>
+  </si>
+  <si>
+    <t>Magnesium glycinate</t>
+  </si>
+  <si>
+    <t>Minerals</t>
+  </si>
+  <si>
+    <t>Low 2-MeOH metabolites (COMT cofactor context), Low cortisol / HPA support context, SEVERE difficulty sleeping symptom</t>
+  </si>
+  <si>
+    <t>COMT cofactor (supports Phase II methylation context) and broad HPA / relaxation / sleep support per published frameworks. Delivers approximately 50 mg elemental magnesium via 50 granules — a conservative in-pod dose; practitioner may consider an additional standalone magnesium top-up to the patient's clinical target if needed.</t>
+  </si>
+  <si>
+    <t>Magnesium-induced loose stools possible at higher elemental doses; glycinate form generally well tolerated.</t>
+  </si>
+  <si>
+    <t>Published literature describes magnesium's role as a COMT cofactor and broader HPA/sleep relevance.</t>
+  </si>
+  <si>
+    <t>W040008000</t>
+  </si>
+  <si>
+    <t>Zinc citrate</t>
+  </si>
+  <si>
+    <t>Low Androgens symptom 31.11%, High Androgens symptom 33.33%</t>
+  </si>
+  <si>
+    <t>Conservative inclusion at ~15 mg elemental zinc given the mixed androgen symptom picture (both High Androgens and Low Androgens categories activated). Zinc supports LH signalling and is described in published literature as relevant to aromatase/5-alpha-reductase modulation.</t>
+  </si>
+  <si>
+    <t>Long-term zinc supplementation &gt;3 months: practitioner to monitor copper status per standard contraindication framework.</t>
+  </si>
+  <si>
+    <t>Published frameworks describe zinc's role in androgen-axis cofactor support — practitioner to assess.</t>
   </si>
   <si>
     <t>W030021000</t>
@@ -194,235 +356,58 @@
     <t>Mitochondrial / Cardiovascular</t>
   </si>
   <si>
-    <t>Total 24hr Cortisol 24.91 ug/gCR (low) — associated energy/fatigue presentation</t>
-  </si>
-  <si>
-    <t>Published literature supports CoQ10 for mitochondrial bioenergetics — for practitioner consideration given HPA-hypocortisolism pattern and associated fatigue presentation.</t>
-  </si>
-  <si>
-    <t>TGA-required label warning advises caution with warfarin. The practitioner may wish to confirm no anticoagulant use.</t>
-  </si>
-  <si>
-    <t>Library entry references for CoQ10 mitochondrial mechanism studies.</t>
-  </si>
-  <si>
-    <t>W030008000</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (methylcobalamin)</t>
-  </si>
-  <si>
-    <t>mcg</t>
-  </si>
-  <si>
-    <t>B-Vitamins / Methylation</t>
-  </si>
-  <si>
-    <t>Low 2-MeOH Estrone (substrate-limited)</t>
-  </si>
-  <si>
-    <t>Methylation cofactor supporting COMT-mediated methylation of catechol oestrogens — for practitioner consideration alongside DIM (which provides 2-OH substrate).</t>
-  </si>
-  <si>
-    <t>Generally well tolerated.</t>
-  </si>
-  <si>
-    <t>Library entry references for methylcobalamin and methylation cycle.</t>
-  </si>
-  <si>
-    <t>W030027000</t>
-  </si>
-  <si>
-    <t>Folate (as calcium folinate)</t>
-  </si>
-  <si>
-    <t>Methylation cofactor at Library AUST L maximum (delivering 500 mcg folinic acid). Supports COMT methylation and overall methylation cycle.</t>
-  </si>
-  <si>
-    <t>Practitioner-only; B12 status should be assured before high-dose folate to avoid masking B12 deficiency. Combined methylcobalamin in this formulation addresses this consideration.</t>
-  </si>
-  <si>
-    <t>Library entry references for calcium folinate and methylation support.</t>
-  </si>
-  <si>
-    <t>W030012000</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (P5P)</t>
-  </si>
-  <si>
-    <t>Low 2-MeOH Estrone (substrate-limited methylation)</t>
-  </si>
-  <si>
-    <t>Methylation cofactor and neurotransmitter/steroid synthesis cofactor — for practitioner consideration in the HPA and methylation context. Dose deliberately conservative given current TGA-required B6 label warnings about peripheral neuropathy.</t>
-  </si>
-  <si>
-    <t>TGA-required label warning regarding peripheral neuropathy with extended high-dose B6. Dose chosen well below regulatory thresholds.</t>
-  </si>
-  <si>
-    <t>Library entry references for P5P methylation and steroidogenesis support.</t>
-  </si>
-  <si>
-    <t>W030011000</t>
-  </si>
-  <si>
-    <t>Riboflavin (B2)</t>
-  </si>
-  <si>
-    <t>Methylation cycle support</t>
-  </si>
-  <si>
-    <t>FAD/FMN cofactor supporting MTHFR and overall methylation cycle — for practitioner consideration as a methylation cofactor adjunct.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; harmless yellow urine discolouration may occur.</t>
-  </si>
-  <si>
-    <t>Library entry references for riboflavin methylation cofactor role.</t>
-  </si>
-  <si>
-    <t>W030004000</t>
-  </si>
-  <si>
-    <t>Pantothenic acid (B5)</t>
-  </si>
-  <si>
-    <t>B5 is the CoA precursor and a specific adrenal cofactor referenced in the laboratory comment for HPA support — for practitioner consideration given the low total urinary cortisol pattern.</t>
-  </si>
-  <si>
-    <t>Generally very well tolerated.</t>
-  </si>
-  <si>
-    <t>Library entry references for pantothenic acid adrenal cofactor role.</t>
-  </si>
-  <si>
-    <t>W030003000</t>
-  </si>
-  <si>
-    <t>Nicotinamide (B3)</t>
-  </si>
-  <si>
-    <t>General redox/energy support</t>
-  </si>
-  <si>
-    <t>NAD precursor supporting energy and redox metabolism — for practitioner consideration as a baseline B-complex cofactor.</t>
-  </si>
-  <si>
-    <t>Nicotinamide form chosen (rather than niacin) — not associated with flushing.</t>
-  </si>
-  <si>
-    <t>Library entry references for nicotinamide and NAD/redox metabolism.</t>
-  </si>
-  <si>
-    <t>W040002000</t>
-  </si>
-  <si>
-    <t>Magnesium glycinate</t>
-  </si>
-  <si>
-    <t>Minerals</t>
-  </si>
-  <si>
-    <t>Low 2-MeOH metabolites (COMT cofactor support), Total 24hr Cortisol 24.91 ug/gCR (low) — HPA support</t>
-  </si>
-  <si>
-    <t>COMT cofactor and HPA support agent. Dose reduced from clinical target (~300 mg elemental Mg) to ~120 mg elemental to fit pod granule budget — for practitioner consideration the patient may benefit from an additional standalone magnesium dose to reach the full clinical target.</t>
-  </si>
-  <si>
-    <t>Generally very well tolerated at this dose; the glycinate form has the lowest osmotic laxative effect.</t>
-  </si>
-  <si>
-    <t>Library entry references for magnesium glycinate, COMT cofactor function, and HPA support.</t>
-  </si>
-  <si>
-    <t>W040008000</t>
-  </si>
-  <si>
-    <t>Zinc citrate</t>
-  </si>
-  <si>
-    <t>Hormone_metabolism axis adjunct, General immune/steroidogenic support</t>
-  </si>
-  <si>
-    <t>Aromatase modulation cofactor and supports steroidogenesis and immune function — moderate dose (~25 mg elemental) chosen deliberately rather than maximum given testosterone is mid-range and androgen-excess pattern is not active.</t>
-  </si>
-  <si>
-    <t>Long-term use of zinc above 25 mg elemental may warrant copper status monitoring per published frameworks. The practitioner may wish to consider copper status at follow-up if used long-term.</t>
-  </si>
-  <si>
-    <t>Library entry references for zinc and aromatase/steroidogenesis modulation.</t>
-  </si>
-  <si>
-    <t>W140010000</t>
-  </si>
-  <si>
-    <t>N-acetyl cysteine (NAC)</t>
-  </si>
-  <si>
-    <t>Antioxidant / Redox</t>
-  </si>
-  <si>
-    <t>Antioxidant buffer for catechol oestrogen metabolism</t>
-  </si>
-  <si>
-    <t>Glutathione precursor and quinone-quenching agent for catechol-oestrogen metabolism — for practitioner consideration as antioxidant support in the oestrogen metabolism context.</t>
-  </si>
-  <si>
-    <t>Library entry references for NAC and glutathione cycling.</t>
-  </si>
-  <si>
-    <t>W010031000</t>
-  </si>
-  <si>
-    <t>Quercetin</t>
-  </si>
-  <si>
-    <t>Flavonoid antioxidant with published mechanism studies for CYP1B1 modulation and antioxidant support — for practitioner consideration as complementary antioxidant in the oestrogen metabolism context.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; may have mild CYP interactions per published literature.</t>
-  </si>
-  <si>
-    <t>Library entry references for quercetin antioxidant and CYP modulation.</t>
+    <t>Total cortisol 24.91 ug/gCR (low) — mitochondrial energy, Metabolic Syndrome symptom 36.67%, MODERATE high blood pressure symptom</t>
+  </si>
+  <si>
+    <t>Dual-relevance inclusion: supports mitochondrial bioenergetics in the context of HPA-hypocortisolism and addresses the cardiometabolic symptom burden (Metabolic Syndrome 36.67%, MODERATE high blood pressure, MILD elevated lipids).</t>
+  </si>
+  <si>
+    <t>TGA-listed warning: practitioner to confirm warfarin status before use per Library entry.</t>
+  </si>
+  <si>
+    <t>Published evidence (Hodgson 2002; Langsjoen series) supports practitioner consideration of CoQ10 for blood pressure and mitochondrial-energy support.</t>
+  </si>
+  <si>
+    <t>W010026000</t>
+  </si>
+  <si>
+    <t>Berberine HCL</t>
+  </si>
+  <si>
+    <t>Blood Glucose / Insulin</t>
+  </si>
+  <si>
+    <t>Metabolic Syndrome symptom 36.67%, SEVERE waist weight gain, MILD elevated triglycerides and high cholesterol</t>
+  </si>
+  <si>
+    <t>Supportive inclusion for the activated Metabolic Syndrome symptom category (36.67%) and waist-weight-gain SEVERE symptom. Approximately 360 mg/day berberine via 36 granules of the standardised extract. Berberine is described in RCT literature for glycaemic and lipid effects.</t>
+  </si>
+  <si>
+    <t>Practitioner to assess medication list (not provided in submission) — berberine has additive effects with glucose-lowering medications and CYP3A4/CYP2D6 interaction potential per standard contraindication framework. Practitioner to confirm no contraindicating medications before initiation.</t>
+  </si>
+  <si>
+    <t>RCT evidence (Yin 2008; Zhang 2008) and meta-analyses (Dong 2013) support practitioner consideration of berberine for glycaemic control and lipid modulation.</t>
   </si>
   <si>
     <t>W030001000</t>
   </si>
   <si>
-    <t>Vitamin C (ascorbic acid)</t>
+    <t>Vitamin C (Ascorbic acid)</t>
   </si>
   <si>
     <t>Vitamin D / C / Neurotransmitter</t>
   </si>
   <si>
-    <t>Total 24hr Cortisol 24.91 ug/gCR (low) — adrenal cofactor</t>
-  </si>
-  <si>
-    <t>Adrenal cofactor specifically referenced in the laboratory comment as supportive in HPA-hypocortisolism, alongside antioxidant function.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated; high doses may cause GI upset.</t>
-  </si>
-  <si>
-    <t>Library entry references for vitamin C and adrenal/antioxidant function.</t>
-  </si>
-  <si>
-    <t>W030005000</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol)</t>
-  </si>
-  <si>
-    <t>General endocrine support</t>
-  </si>
-  <si>
-    <t>General endocrine support at Library AUST L maximum (1000 IU). Published literature supports vitamin D adequacy as relevant to overall endocrine and immune function.</t>
-  </si>
-  <si>
-    <t>Generally well tolerated at this dose. The practitioner may wish to confirm 25-OH vitamin D status if not recently assessed.</t>
-  </si>
-  <si>
-    <t>Library entry references for vitamin D3.</t>
+    <t>Total cortisol 24.91 ug/gCR (low), Low Cortisol symptom 28.57%</t>
+  </si>
+  <si>
+    <t>Classical adrenal cofactor support for the HPA-hypocortisolism pattern; the adrenal cortex is described as containing one of the highest ascorbate concentrations in the body per published literature.</t>
+  </si>
+  <si>
+    <t>Generally well tolerated at 500 mg; higher doses may cause GI discomfort.</t>
+  </si>
+  <si>
+    <t>Published frameworks describe vitamin C as an adrenal cofactor — practitioner to assess.</t>
   </si>
   <si>
     <t>Adjustment Type</t>
@@ -434,25 +419,16 @@
     <t>Affected Ingredient(s)</t>
   </si>
   <si>
-    <t>Dose reduced for pod budget</t>
-  </si>
-  <si>
-    <t>Magnesium glycinate proposed at 1023.5 mg salt (delivering ~120 mg elemental Mg), reduced from a clinical target of ~300 mg elemental Mg (~2562 mg salt) due to pod granule budget constraints. The practitioner may wish to consider an additional standalone magnesium dose if the patient benefits from the higher target.</t>
-  </si>
-  <si>
-    <t>Conservative dose by clinical choice</t>
-  </si>
-  <si>
-    <t>Zinc citrate proposed at ~25 mg elemental rather than the Library maximum of 50 mg elemental — deliberately conservative given testosterone is mid-range and androgen-excess pattern is not active. The practitioner may wish to adjust based on copper:zinc considerations and clinical correlation.</t>
-  </si>
-  <si>
-    <t>Regulatory cap</t>
-  </si>
-  <si>
-    <t>Calcium folinate dosed at Library AUST L maximum of 547 mcg salt (500 mcg folinic acid). Resveratrol dosed at Library AUST L maximum of 150 mg. Vitamin D3 dosed at Library AUST L maximum of 25 mcg (1000 IU). Vitamin B6 dosed conservatively at 10 mg elemental given TGA-required peripheral neuropathy label warnings for higher doses.</t>
-  </si>
-  <si>
-    <t>Calcium folinate, Resveratrol, Vitamin D3, Vitamin B6 (P5P)</t>
+    <t>pod_budget_reduction_below_clinical_target</t>
+  </si>
+  <si>
+    <t>Magnesium glycinate has been included in the pod at 50 mg elemental Mg (~50 granules) versus a clinical target of 200 mg elemental Mg. This is a deliberate pod-budget choice — the in-pod dose is conservative but clinically meaningful, and the practitioner may consider an additional standalone magnesium glycinate top-up of approximately 150 mg elemental Mg if the patient's clinical context (sleep, HPA, BP) supports it.</t>
+  </si>
+  <si>
+    <t>Rhodiola dose set at 150 mg (clinical target 300 mg) reflects both pod-budget allocation and the explicit clinical caution about autonomic-arousal symptoms; the lower dose is intentional rather than purely budget-driven.</t>
+  </si>
+  <si>
+    <t>American ginseng dose set at 200 mg (clinical target 400 mg) reflects pod-budget allocation; practitioner may consider standalone top-up if clinically indicated.</t>
   </si>
   <si>
     <t>Recommendation</t>
@@ -464,67 +440,118 @@
     <t>Practitioner Note</t>
   </si>
   <si>
-    <t>(none)</t>
+    <t>Phosphatidylserine 100–200 mg daily (not currently in Library)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>For practitioner consideration in HPA-hypocortisolism / sleep-disrupted patterns. Published literature describes phosphatidylserine's potential cortisol-pattern modulation effects — practitioner to assess clinical relevance.</t>
+  </si>
+  <si>
+    <t>Omega-3 EPA/DHA fish oil (not currently in Library)</t>
+  </si>
+  <si>
+    <t>For practitioner consideration given the cardiometabolic symptom burden (elevated triglycerides, high cholesterol, BP). Standard dosing 2–3 g combined EPA/DHA daily per integrative medicine frameworks.</t>
+  </si>
+  <si>
+    <t>Comprehensive standard cardiometabolic biomarker panel (fasting glucose, HbA1c, full lipid profile, lipoprotein subfractions, hsCRP, fasting insulin)</t>
+  </si>
+  <si>
+    <t>Given that the Metabolic Syndrome symptom category scores 36.67% with SEVERE waist weight gain and MODERATE BP, the practitioner may wish to confirm/quantify cardiometabolic biomarkers, which are not included on the EndoSCAN panel.</t>
+  </si>
+  <si>
+    <t>Thyroid panel including anti-TPO and anti-Tg antibodies plus FT3, FT4, TSH, Reverse T3</t>
+  </si>
+  <si>
+    <t>Hypometabolism symptom category 29.17% activates a thyroid-axis question that this panel does not address. Antibody status is also relevant to the iodine binding-exclusion decision.</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>informational</t>
+  </si>
+  <si>
+    <t>Medication list not provided in submission</t>
+  </si>
+  <si>
+    <t>The submission did not list current medications. Standard contraindication checks (5-HTP/serotonergic medications, berberine/glucose-lowering medications, berberine/CYP3A4 and CYP2D6 substrates, magnesium/antibiotics + bisphosphonates, vitamin K/anticoagulants, curcumin/anticoagulants, NAC long-term/trace minerals) are based on the formulation alone. The practitioner should clear the proposed formulation against the patient's actual medication list before dispensing.</t>
+  </si>
+  <si>
+    <t>Berberine HCL (Indian Barberry), Magnesium glycinate, Coenzyme Q10, Resveratrol, N-acetyl cysteine (NAC)</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>Berberine — glucose-lowering medication interaction</t>
+  </si>
+  <si>
+    <t>If the patient is on glucose-lowering pharmaceuticals, berberine may have additive effects per published pharmacology. Practitioner to confirm no contraindicating medications before dispensing.</t>
+  </si>
+  <si>
+    <t>Berberine HCL (Indian Barberry)</t>
+  </si>
+  <si>
+    <t>Berberine — CYP3A4/CYP2D6 substrate interaction</t>
+  </si>
+  <si>
+    <t>Berberine has documented pharmacokinetic interaction potential with CYP3A4 and CYP2D6 substrates per published literature. Practitioner to assess.</t>
+  </si>
+  <si>
+    <t>CoQ10 — warfarin</t>
+  </si>
+  <si>
+    <t>TGA-listed warning per Library entry: 'Do not take while on warfarin therapy without medical advice.' Practitioner to confirm warfarin status before dispensing.</t>
+  </si>
+  <si>
+    <t>Resveratrol — anticoagulants</t>
+  </si>
+  <si>
+    <t>TGA-listed warning per Library entry: 'Resveratrol may affect the way some medicines work, including Warfarin.' Practitioner to confirm anticoagulant status.</t>
+  </si>
+  <si>
+    <t>monitor</t>
+  </si>
+  <si>
+    <t>Zinc — long-term copper ratio</t>
+  </si>
+  <si>
+    <t>If zinc supplementation continues &gt;3 months, the practitioner may wish to monitor copper status per the standard contraindication framework. Conservative dose at 15 mg elemental keeps this risk low.</t>
+  </si>
+  <si>
+    <t>applied</t>
+  </si>
+  <si>
+    <t>Licorice / Glycyrrhiza — binding exclusion applied</t>
+  </si>
+  <si>
+    <t>Symptom-driven binding exclusion applied due to MODERATE 'high blood pressure' symptom and cardiometabolic burden — ingredient excluded from pod and from standalone recommendations.</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
-    <t>No standalone recommendations or pod exclusions on this formulation.</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
-    <t>informational</t>
-  </si>
-  <si>
-    <t>No medication context provided</t>
-  </si>
-  <si>
-    <t>Practitioner's clinical notes did not list current medications. Standard contraindication checks are therefore based on the formulation alone. The practitioner may wish to confirm absence of: anticoagulants (relevant to resveratrol and CoQ10 per TGA warnings), thyroid medications (relevant to ashwagandha caution), immunosuppressants (relevant to adaptogens), glucose-lowering agents (relevant to American ginseng), antihypertensives (relevant to American ginseng), and CYP3A4/2D6 substrates.</t>
-  </si>
-  <si>
-    <t>moderate</t>
-  </si>
-  <si>
-    <t>Resveratrol — warfarin interaction risk</t>
-  </si>
-  <si>
-    <t>TGA-required label warning notes resveratrol may affect anticoagulants including warfarin. Confirm patient is not on anticoagulants before recommending.</t>
-  </si>
-  <si>
-    <t>CoQ10 — warfarin interaction risk</t>
-  </si>
-  <si>
-    <t>TGA-required label warning notes caution with warfarin therapy. Confirm patient is not on anticoagulants before recommending.</t>
-  </si>
-  <si>
-    <t>monitor</t>
-  </si>
-  <si>
-    <t>Vitamin B6 peripheral neuropathy</t>
-  </si>
-  <si>
-    <t>TGA-required label warning advises monitoring for tingling, burning, or numbness with vitamin B6 use. Dose in this formulation is conservative (10 mg pyridoxine equivalent) and well below regulatory thresholds, but the practitioner may wish to monitor on follow-up.</t>
-  </si>
-  <si>
-    <t>Long-term zinc and copper status</t>
-  </si>
-  <si>
-    <t>Zinc at 25 mg elemental long-term (&gt;3 months) warrants practitioner consideration of copper status per standard frameworks. Re-test or clinical review at appropriate intervals.</t>
-  </si>
-  <si>
-    <t>applied</t>
-  </si>
-  <si>
-    <t>Iodine — binding exclusion applied</t>
-  </si>
-  <si>
-    <t>Iodine above 150 mcg not included given absence of thyroid antibody data on this panel. No iodine included in formulation as no thyroid driver is activated.</t>
+    <t>High-dose iodine — binding exclusion applied</t>
+  </si>
+  <si>
+    <t>Symptom-driven binding exclusion applied due to thyroid-related symptom category ≥20% with antibody status unknown on this panel. No iodine included.</t>
+  </si>
+  <si>
+    <t>Mixed androgen symptom signal</t>
+  </si>
+  <si>
+    <t>Both Low Androgens (31.11%) and High Androgens (33.33%) symptom categories are activated. Practitioner to correlate with clinical presentation and any serum testosterone/SHBG data; the formulation takes a conservative middle-ground approach (moderate zinc, no saw palmetto, ashwagandha for general androgen-axis support).</t>
+  </si>
+  <si>
+    <t>Cardiometabolic axis driven by symptom data only</t>
+  </si>
+  <si>
+    <t>blood_glucose_insulin and parts of mitochondrial_cardiovascular axes are driven by symptom matrix without measured fasting glucose/lipid biomarkers on this panel — practitioner may wish to confirm with standard biomarker testing before extended use.</t>
   </si>
   <si>
     <t/>
@@ -542,13 +569,13 @@
     <t>Pod budget utilisation</t>
   </si>
   <si>
-    <t>96.1%</t>
+    <t>92.7%</t>
   </si>
   <si>
     <t>Pod weight (estimated)</t>
   </si>
   <si>
-    <t>13,101 mg</t>
+    <t>12,710 mg</t>
   </si>
   <si>
     <t>Ingredients in pod</t>
@@ -584,16 +611,19 @@
     <t>Thyroid / Adaptogenic (primary)</t>
   </si>
   <si>
+    <t>Antioxidant / Redox (secondary)</t>
+  </si>
+  <si>
     <t>B-Vitamins / Methylation (secondary)</t>
   </si>
   <si>
+    <t>Minerals (secondary)</t>
+  </si>
+  <si>
     <t>Mitochondrial / Cardiovascular (secondary)</t>
   </si>
   <si>
-    <t>Antioxidant / Redox (secondary)</t>
-  </si>
-  <si>
-    <t>Minerals (secondary)</t>
+    <t>Blood Glucose / Insulin (supportive)</t>
   </si>
   <si>
     <t>Vitamin D / C / Neurotransmitter (supportive)</t>
@@ -625,8 +655,8 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF666666"/>
+      <b/>
+      <color rgb="FF8B2A2A"/>
       <sz val="10"/>
       <name val="Roboto"/>
     </font>
@@ -703,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -720,7 +750,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1093,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1151,13 +1186,13 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>14</v>
@@ -1186,48 +1221,48 @@
         <v>21</v>
       </c>
       <c r="C3" s="5">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="5">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
@@ -1236,24 +1271,24 @@
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5">
         <v>150</v>
@@ -1262,313 +1297,313 @@
         <v>13</v>
       </c>
       <c r="E5" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" s="5">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="5">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="5">
-        <v>547</v>
+        <v>500</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E11" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3">
-        <v>15.68</v>
+        <v>547</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5">
-        <v>20</v>
+        <v>7.84</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3">
         <v>218.4</v>
@@ -1580,267 +1615,197 @@
         <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C15" s="5">
-        <v>50</v>
+        <v>427.5</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C16" s="3">
-        <v>1023.5</v>
+        <v>46.725</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C17" s="5">
-        <v>77.62</v>
+        <v>100</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="5">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3">
-        <v>500</v>
+        <v>379.08</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="3">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>15</v>
+        <v>119</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C19" s="5">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="5">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="3">
-        <v>500</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="3">
-        <v>50</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="5">
-        <v>25</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="5">
-        <v>2</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1861,46 +1826,46 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1911,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1921,24 +1886,57 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1949,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1960,49 +1958,49 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>157</v>
+      <c r="A4" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>160</v>
@@ -2011,49 +2009,105 @@
         <v>161</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>150</v>
+      <c r="B8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2118,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2073,178 +2127,186 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>171</v>
+      <c r="A2" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>170</v>
+      <c r="A4" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="13">
-        <v>682</v>
+      <c r="A5" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="14">
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>175</v>
+      <c r="A6" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>177</v>
+      <c r="A7" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="15">
-        <v>20</v>
+      <c r="A8" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="16">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>170</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>186</v>
+      <c r="A17" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="18">
-        <v>180</v>
+      <c r="A18" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="19">
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="19">
-        <v>70</v>
+      <c r="A19" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="20">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="18">
+      <c r="A20" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="19">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="20">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="19">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="20">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="18">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B23" s="19">
-        <v>145</v>
-      </c>
-    </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="18">
-        <v>55</v>
+      <c r="A24" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="19">
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" s="21">
-        <v>780</v>
+      <c r="A25" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B26" s="22">
+        <v>633</v>
       </c>
     </row>
   </sheetData>
